--- a/data/trans_orig/P19D-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19D-Clase-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>333990</t>
+          <t>333921</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>358778</t>
+          <t>358065</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236129</t>
+          <t>236383</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254320</t>
+          <t>254325</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>578830</t>
+          <t>577713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>608920</t>
+          <t>607517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13880</t>
+          <t>14423</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31892</t>
+          <t>32633</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21354</t>
+          <t>22197</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25551</t>
+          <t>25814</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48152</t>
+          <t>47427</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>10526</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29146</t>
+          <t>28903</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15419</t>
+          <t>15695</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16585</t>
+          <t>16473</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38022</t>
+          <t>39080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>253107</t>
+          <t>252575</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>276743</t>
+          <t>276417</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>300125</t>
+          <t>301570</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>319466</t>
+          <t>319009</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>559720</t>
+          <t>561676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>591940</t>
+          <t>591032</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28453</t>
+          <t>29015</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18681</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>18694</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41019</t>
+          <t>41508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26586</t>
+          <t>28445</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21050</t>
+          <t>19959</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18195</t>
+          <t>18460</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42009</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>383090</t>
+          <t>382735</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>405332</t>
+          <t>404763</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>121031</t>
+          <t>120397</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>134299</t>
+          <t>133964</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>509854</t>
+          <t>510548</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>535747</t>
+          <t>535890</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13315</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21495</t>
+          <t>22516</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43307</t>
+          <t>42645</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15628</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28404</t>
+          <t>28806</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52670</t>
+          <t>52665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>9149</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>10688</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>774259</t>
+          <t>775940</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>809833</t>
+          <t>808619</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>533361</t>
+          <t>532294</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>562091</t>
+          <t>560506</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1318799</t>
+          <t>1316568</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1361843</t>
+          <t>1360326</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,63%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15988</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13593</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>23034</t>
+          <t>25679</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53691</t>
+          <t>54186</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86714</t>
+          <t>85141</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>27869</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53892</t>
+          <t>53206</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89393</t>
+          <t>90028</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129276</t>
+          <t>131505</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>196090</t>
+          <t>197919</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>219519</t>
+          <t>220015</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>403835</t>
+          <t>404172</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>427962</t>
+          <t>429287</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>610361</t>
+          <t>611070</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>642839</t>
+          <t>644692</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12099</t>
+          <t>11469</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26523</t>
+          <t>26016</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>49881</t>
+          <t>48337</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>23136</t>
+          <t>22668</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>45647</t>
+          <t>45584</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>54664</t>
+          <t>53670</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>86134</t>
+          <t>86224</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>197147</t>
+          <t>197125</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>207836</t>
+          <t>208447</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>826570</t>
+          <t>827388</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>864195</t>
+          <t>862970</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1028734</t>
+          <t>1027589</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1068021</t>
+          <t>1068804</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24083</t>
+          <t>24023</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>26142</t>
+          <t>26490</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12879</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>66162</t>
+          <t>66013</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>101732</t>
+          <t>99997</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>70883</t>
+          <t>72155</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>107637</t>
+          <t>108456</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>15045</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,47 +4197,47 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>9431</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>4903</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>17952</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>9431</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>4236</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>17301</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2183861</t>
+          <t>2189580</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2241888</t>
+          <t>2246967</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2465680</t>
+          <t>2468454</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2527825</t>
+          <t>2527251</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4670656</t>
+          <t>4670232</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4758327</t>
+          <t>4752690</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>42585</t>
+          <t>42175</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>74405</t>
+          <t>72128</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>37275</t>
+          <t>37113</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>63966</t>
+          <t>65409</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>86176</t>
+          <t>87244</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>127727</t>
+          <t>128083</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>152131</t>
+          <t>151368</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>204155</t>
+          <t>201362</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>159750</t>
+          <t>158155</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>212681</t>
+          <t>211946</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>323440</t>
+          <t>328514</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>398059</t>
+          <t>399414</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -5063,12 +5063,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>338323</t>
+          <t>336029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>364998</t>
+          <t>364494</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246605</t>
+          <t>246556</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269593</t>
+          <t>269439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>592493</t>
+          <t>592053</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>629236</t>
+          <t>628375</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>17868</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42735</t>
+          <t>42752</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27925</t>
+          <t>29239</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31878</t>
+          <t>32877</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63743</t>
+          <t>62324</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22002</t>
+          <t>21854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23245</t>
+          <t>23905</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17759</t>
+          <t>17973</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39966</t>
+          <t>40130</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>305230</t>
+          <t>304645</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>337263</t>
+          <t>336926</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>267435</t>
+          <t>266780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>291505</t>
+          <t>292041</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>581673</t>
+          <t>580592</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>622211</t>
+          <t>622311</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,39%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39831</t>
+          <t>41035</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>21065</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26521</t>
+          <t>27503</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55484</t>
+          <t>54523</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21001</t>
+          <t>20437</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46589</t>
+          <t>45611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>12241</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>31479</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38922</t>
+          <t>39286</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>71346</t>
+          <t>74245</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>436216</t>
+          <t>437275</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>469971</t>
+          <t>470308</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>203845</t>
+          <t>204848</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>223470</t>
+          <t>223695</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>646189</t>
+          <t>648939</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>688531</t>
+          <t>688189</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,76%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23266</t>
+          <t>22858</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19260</t>
+          <t>19528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37044</t>
+          <t>36731</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54098</t>
+          <t>52068</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85926</t>
+          <t>84712</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7983</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23955</t>
+          <t>23941</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63892</t>
+          <t>65854</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101836</t>
+          <t>102283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>752802</t>
+          <t>751765</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>803601</t>
+          <t>804729</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>597547</t>
+          <t>596730</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>633367</t>
+          <t>633757</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1360268</t>
+          <t>1364890</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1425920</t>
+          <t>1424580</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21533</t>
+          <t>23257</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14817</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>34453</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>152671</t>
+          <t>151860</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>202170</t>
+          <t>204380</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51802</t>
+          <t>51328</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84983</t>
+          <t>86032</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>213092</t>
+          <t>214227</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>275124</t>
+          <t>273712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>294761</t>
+          <t>294310</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>329303</t>
+          <t>328511</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>533229</t>
+          <t>535719</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>573887</t>
+          <t>573744</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>838476</t>
+          <t>838747</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>891567</t>
+          <t>890290</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,89%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>13437</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>14507</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>23788</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>67018</t>
+          <t>68639</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>100414</t>
+          <t>100534</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>90639</t>
+          <t>90231</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>131618</t>
+          <t>128616</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>170073</t>
+          <t>170935</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>219316</t>
+          <t>221040</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>177719</t>
+          <t>178185</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>201617</t>
+          <t>200339</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>762266</t>
+          <t>762751</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>807333</t>
+          <t>807125</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>951683</t>
+          <t>951965</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1001061</t>
+          <t>1003180</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,41%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21750</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>12918</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>31507</t>
+          <t>31404</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>20159</t>
+          <t>20267</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>45119</t>
+          <t>44970</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13400</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>32336</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>100143</t>
+          <t>98937</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>143126</t>
+          <t>141265</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>119135</t>
+          <t>117227</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>163058</t>
+          <t>161791</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2369735</t>
+          <t>2365294</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2450280</t>
+          <t>2450503</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2674917</t>
+          <t>2674805</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2751859</t>
+          <t>2752810</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5069319</t>
+          <t>5066633</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5187481</t>
+          <t>5185786</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>77345</t>
+          <t>77848</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>119557</t>
+          <t>120231</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>62842</t>
+          <t>63898</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>104924</t>
+          <t>101802</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>151162</t>
+          <t>148611</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>211824</t>
+          <t>206007</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>360974</t>
+          <t>358231</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>434152</t>
+          <t>437593</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>307661</t>
+          <t>308417</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>377871</t>
+          <t>380215</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>680641</t>
+          <t>684986</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>790418</t>
+          <t>793960</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -9280,12 +9280,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>335331</t>
+          <t>335204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>359238</t>
+          <t>359588</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266697</t>
+          <t>265070</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289310</t>
+          <t>289901</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>607611</t>
+          <t>609581</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>643087</t>
+          <t>645120</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32049</t>
+          <t>30407</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30554</t>
+          <t>30718</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29709</t>
+          <t>28575</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55191</t>
+          <t>55254</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -9506,12 +9506,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10212</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26495</t>
+          <t>27799</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>24664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21644</t>
+          <t>21469</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>44461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>263050</t>
+          <t>262866</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>287225</t>
+          <t>287492</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>279761</t>
+          <t>279457</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>303518</t>
+          <t>303941</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>550152</t>
+          <t>552536</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>584940</t>
+          <t>584348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -9962,12 +9962,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>9732</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27895</t>
+          <t>27135</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34637</t>
+          <t>34408</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29521</t>
+          <t>28783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54635</t>
+          <t>54582</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -10075,12 +10075,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13514</t>
+          <t>13437</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31735</t>
+          <t>32284</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10493</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28969</t>
+          <t>27557</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28255</t>
+          <t>28741</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53911</t>
+          <t>53744</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -10418,12 +10418,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>350505</t>
+          <t>351668</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>376376</t>
+          <t>375585</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10433,12 +10433,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>113505</t>
+          <t>113690</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>129068</t>
+          <t>128932</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>470420</t>
+          <t>470265</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>499475</t>
+          <t>501386</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>10391</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13853</t>
+          <t>13573</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -10644,12 +10644,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25687</t>
+          <t>26425</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50379</t>
+          <t>49123</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22674</t>
+          <t>22771</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39459</t>
+          <t>38996</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68192</t>
+          <t>67461</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>780605</t>
+          <t>781371</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>814305</t>
+          <t>816804</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>583922</t>
+          <t>583558</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>618741</t>
+          <t>618022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1378108</t>
+          <t>1377609</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1427345</t>
+          <t>1424688</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -11100,12 +11100,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>13066</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11135,12 +11135,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23628</t>
+          <t>24574</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11150,12 +11150,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29358</t>
+          <t>30708</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58362</t>
+          <t>57690</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91581</t>
+          <t>92353</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52865</t>
+          <t>52946</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84797</t>
+          <t>84281</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11263,12 +11263,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>118036</t>
+          <t>119049</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>165135</t>
+          <t>165143</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>338935</t>
+          <t>339672</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>372777</t>
+          <t>370216</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>480338</t>
+          <t>480638</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>510722</t>
+          <t>511494</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>827562</t>
+          <t>828691</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>871171</t>
+          <t>872726</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -11669,12 +11669,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13953</t>
+          <t>13083</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18044</t>
+          <t>18992</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>48926</t>
+          <t>50779</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>81374</t>
+          <t>80277</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11797,12 +11797,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>41617</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>69975</t>
+          <t>70606</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>99477</t>
+          <t>99484</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>142853</t>
+          <t>141948</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -12125,12 +12125,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>195404</t>
+          <t>195442</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>218568</t>
+          <t>218698</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12160,12 +12160,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>698560</t>
+          <t>700271</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>737779</t>
+          <t>738795</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>904526</t>
+          <t>903871</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>947929</t>
+          <t>949751</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,13%</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7770</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12273,12 +12273,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>35286</t>
+          <t>35155</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>37362</t>
+          <t>36533</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -12351,12 +12351,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>21532</t>
+          <t>21030</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>43230</t>
+          <t>43143</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>67280</t>
+          <t>66088</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>102394</t>
+          <t>100782</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>95995</t>
+          <t>95621</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>134443</t>
+          <t>136254</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -12581,12 +12581,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10398</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2317120</t>
+          <t>2318006</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2383444</t>
+          <t>2385012</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2474197</t>
+          <t>2473038</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2546090</t>
+          <t>2544450</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12764,12 +12764,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4818703</t>
+          <t>4819510</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4914047</t>
+          <t>4913576</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>37421</t>
+          <t>39053</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>68356</t>
+          <t>68817</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>69916</t>
+          <t>69976</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>108476</t>
+          <t>109393</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>115968</t>
+          <t>118506</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>165206</t>
+          <t>168455</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>218403</t>
+          <t>214760</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>278139</t>
+          <t>277337</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>221084</t>
+          <t>223229</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>283402</t>
+          <t>284359</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>453942</t>
+          <t>456456</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>538532</t>
+          <t>541856</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -13492,32 +13492,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>467110</t>
+          <t>507807</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452016</t>
+          <t>494081</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>476966</t>
+          <t>518870</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13527,32 +13527,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>421190</t>
+          <t>456907</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>412083</t>
+          <t>446815</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427200</t>
+          <t>464740</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13562,32 +13562,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>888301</t>
+          <t>964714</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>872365</t>
+          <t>947347</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>900434</t>
+          <t>977578</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -13605,32 +13605,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11954</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30022</t>
+          <t>29371</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13640,32 +13640,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18114</t>
+          <t>24862</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13675,32 +13675,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>31043</t>
+          <t>35310</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>25708</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42208</t>
+          <t>49968</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -13718,32 +13718,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>9368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>29995</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13753,32 +13753,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>10805</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15596</t>
+          <t>17095</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13788,27 +13788,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>24126</t>
+          <t>26929</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>18433</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36930</t>
+          <t>40108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -13831,17 +13831,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>500598</t>
+          <t>543571</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>500598</t>
+          <t>543571</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500598</t>
+          <t>543571</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13866,17 +13866,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>442871</t>
+          <t>483382</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>442871</t>
+          <t>483382</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>442871</t>
+          <t>483382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13901,17 +13901,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>943470</t>
+          <t>1026953</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>943470</t>
+          <t>1026953</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>943470</t>
+          <t>1026953</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14061,32 +14061,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>419250</t>
+          <t>446950</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>406278</t>
+          <t>433994</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>427873</t>
+          <t>456135</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14096,32 +14096,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>361015</t>
+          <t>398575</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>352834</t>
+          <t>391624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>366926</t>
+          <t>405283</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14131,32 +14131,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>780265</t>
+          <t>845525</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>767131</t>
+          <t>830470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>791645</t>
+          <t>857295</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -14174,22 +14174,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>17517</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27521</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14209,32 +14209,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12145</t>
+          <t>12656</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14244,32 +14244,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>23224</t>
+          <t>24741</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15473</t>
+          <t>16209</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34660</t>
+          <t>36510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -14287,102 +14287,102 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>9393</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22110</t>
+          <t>25005</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,21%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>11375</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6683</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>17982</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>27043</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>36857</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
           <t>3,01%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10310</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5798</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>17003</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>23833</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>16186</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>34609</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -14400,17 +14400,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>449210</t>
+          <t>480135</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>449210</t>
+          <t>480135</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>449210</t>
+          <t>480135</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14435,17 +14435,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>378112</t>
+          <t>417174</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>378112</t>
+          <t>417174</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>378112</t>
+          <t>417174</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14470,17 +14470,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>827322</t>
+          <t>897309</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>827322</t>
+          <t>897309</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>827322</t>
+          <t>897309</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14630,32 +14630,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>378779</t>
+          <t>420165</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>150949</t>
+          <t>403897</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>607733</t>
+          <t>432358</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14665,32 +14665,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>156813</t>
+          <t>175080</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>150238</t>
+          <t>168679</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>160645</t>
+          <t>179167</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14700,32 +14700,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>535592</t>
+          <t>595245</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>243591</t>
+          <t>579657</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>766983</t>
+          <t>608455</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -14743,32 +14743,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>7234</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13754</t>
+          <t>15036</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14778,22 +14778,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14813,32 +14813,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9122</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18294</t>
+          <t>19454</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -14856,32 +14856,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>276717</t>
+          <t>37409</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44904</t>
+          <t>26057</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>507085</t>
+          <t>53332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14891,32 +14891,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>13222</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -14926,32 +14926,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>283148</t>
+          <t>44883</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47482</t>
+          <t>33297</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>579003</t>
+          <t>61004</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -14969,17 +14969,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>661703</t>
+          <t>464808</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>661703</t>
+          <t>464808</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>661703</t>
+          <t>464808</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15004,17 +15004,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166159</t>
+          <t>186143</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166159</t>
+          <t>186143</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166159</t>
+          <t>186143</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>827862</t>
+          <t>650950</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>827862</t>
+          <t>650950</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>827862</t>
+          <t>650950</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15199,32 +15199,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>911169</t>
+          <t>988987</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>890612</t>
+          <t>966308</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>926707</t>
+          <t>1007726</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15234,32 +15234,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>920573</t>
+          <t>790588</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>903156</t>
+          <t>777017</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>938381</t>
+          <t>801395</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15269,32 +15269,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1831741</t>
+          <t>1779576</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1804507</t>
+          <t>1752711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1872483</t>
+          <t>1801991</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -15312,67 +15312,67 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>15880</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>8391</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>4380</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>19304</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>6577</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>2436</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>16997</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15382,32 +15382,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>11727</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>8696</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22159</t>
+          <t>25858</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -15425,32 +15425,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>83376</t>
+          <t>100360</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67499</t>
+          <t>82926</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103250</t>
+          <t>123836</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15460,32 +15460,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>31566</t>
+          <t>36418</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15815</t>
+          <t>27004</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45083</t>
+          <t>46600</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15495,32 +15495,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>114942</t>
+          <t>136778</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78010</t>
+          <t>116037</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139980</t>
+          <t>162797</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -15538,17 +15538,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>999694</t>
+          <t>1096068</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>999694</t>
+          <t>1096068</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>999694</t>
+          <t>1096068</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15573,17 +15573,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>958716</t>
+          <t>835398</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>958716</t>
+          <t>835398</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>958716</t>
+          <t>835398</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15608,17 +15608,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1958410</t>
+          <t>1931466</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1958410</t>
+          <t>1931466</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1958410</t>
+          <t>1931466</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15768,32 +15768,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>354903</t>
+          <t>410601</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>334112</t>
+          <t>388583</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>370462</t>
+          <t>428247</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15803,32 +15803,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>746195</t>
+          <t>720802</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>725858</t>
+          <t>706433</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>764462</t>
+          <t>734774</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15838,32 +15838,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1101098</t>
+          <t>1131403</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1072071</t>
+          <t>1103603</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1130109</t>
+          <t>1153340</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15916,32 +15916,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>9677</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15951,32 +15951,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>13081</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -15994,32 +15994,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>82109</t>
+          <t>95751</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>66503</t>
+          <t>78119</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>102924</t>
+          <t>117955</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16029,32 +16029,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>66771</t>
+          <t>71413</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>49184</t>
+          <t>57870</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>87517</t>
+          <t>85618</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16064,32 +16064,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>148880</t>
+          <t>167164</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>120234</t>
+          <t>145635</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>178329</t>
+          <t>192930</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -16107,17 +16107,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>437177</t>
+          <t>508089</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>437177</t>
+          <t>508089</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>437177</t>
+          <t>508089</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16142,17 +16142,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>816366</t>
+          <t>796516</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>816366</t>
+          <t>796516</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>816366</t>
+          <t>796516</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16177,17 +16177,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1253543</t>
+          <t>1304606</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1253543</t>
+          <t>1304606</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1253543</t>
+          <t>1304606</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16209,7 +16209,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -16337,32 +16337,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>204242</t>
+          <t>200342</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>183091</t>
+          <t>179627</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>217418</t>
+          <t>211194</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16372,32 +16372,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>681068</t>
+          <t>749983</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>665038</t>
+          <t>734580</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>693133</t>
+          <t>763210</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16407,32 +16407,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>885310</t>
+          <t>950324</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>857774</t>
+          <t>927129</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>903723</t>
+          <t>968120</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -16450,32 +16450,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>7794</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2381</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21187</t>
+          <t>19873</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16485,67 +16485,67 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17823</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>11230</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>5018</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>24980</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
           <t>2,4%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>12051</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>5316</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>26923</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -16563,32 +16563,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>18440</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>41905</t>
+          <t>31065</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16598,32 +16598,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>56112</t>
+          <t>63042</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>45070</t>
+          <t>50329</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>69799</t>
+          <t>78282</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16633,32 +16633,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>74552</t>
+          <t>77462</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>58821</t>
+          <t>61968</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>99376</t>
+          <t>99562</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -16676,17 +16676,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>229853</t>
+          <t>222556</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>229853</t>
+          <t>222556</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>229853</t>
+          <t>222556</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -16711,17 +16711,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>742060</t>
+          <t>816461</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>742060</t>
+          <t>816461</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>742060</t>
+          <t>816461</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -16746,17 +16746,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>971913</t>
+          <t>1039016</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>971913</t>
+          <t>1039016</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>971913</t>
+          <t>1039016</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -16906,32 +16906,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2735453</t>
+          <t>2974851</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2107378</t>
+          <t>2931814</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2962220</t>
+          <t>3008729</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16941,32 +16941,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3286854</t>
+          <t>3291935</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3255087</t>
+          <t>3266198</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3326610</t>
+          <t>3316473</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16976,32 +16976,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>6022307</t>
+          <t>6266787</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5206441</t>
+          <t>6217207</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6266962</t>
+          <t>6312292</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -17019,32 +17019,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>54345</t>
+          <t>60643</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>38085</t>
+          <t>45520</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>73812</t>
+          <t>80557</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17054,32 +17054,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>36386</t>
+          <t>42612</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>27430</t>
+          <t>32453</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>49990</t>
+          <t>56971</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17089,32 +17089,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>90730</t>
+          <t>103254</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>71436</t>
+          <t>84385</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>115435</t>
+          <t>127263</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -17132,32 +17132,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>488438</t>
+          <t>279732</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>256903</t>
+          <t>246910</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1133410</t>
+          <t>317785</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17167,32 +17167,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>181043</t>
+          <t>200527</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>145145</t>
+          <t>178439</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>210053</t>
+          <t>224201</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17202,32 +17202,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>669482</t>
+          <t>480259</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>423666</t>
+          <t>440362</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1479939</t>
+          <t>526132</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -17245,17 +17245,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3278236</t>
+          <t>3315226</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3278236</t>
+          <t>3315226</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3278236</t>
+          <t>3315226</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17280,17 +17280,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3504283</t>
+          <t>3535074</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3504283</t>
+          <t>3535074</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3504283</t>
+          <t>3535074</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17315,17 +17315,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6782519</t>
+          <t>6850300</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6782519</t>
+          <t>6850300</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6782519</t>
+          <t>6850300</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
